--- a/excel/output_stats_vfvv/atax/PerSubgraphStats.xlsx
+++ b/excel/output_stats_vfvv/atax/PerSubgraphStats.xlsx
@@ -529,7 +529,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
         <v>63</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>46</v>
@@ -670,7 +670,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>51</v>
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>13</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>20</v>
@@ -1093,7 +1093,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2992170</v>
+        <v>12456300</v>
       </c>
       <c r="K14" t="n">
         <v>58778000</v>
@@ -1187,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1925</v>
+        <v>2975</v>
       </c>
       <c r="K16" t="n">
         <v>16800</v>
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
         <v>36</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>15237400</v>
+        <v>15238400</v>
       </c>
       <c r="K19" t="n">
         <v>66101700</v>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
         <v>44</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
         <v>71</v>
